--- a/storage/app/templates/payment.xlsx
+++ b/storage/app/templates/payment.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eXWFei8AXJt9cUEBgleaxG7DvVNiSnmC53zB+Bbdqjo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="T4KbICPeEJwl/82gsdVrvcUbw7YoA1tLLCRZc3XVC0I="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Payment</t>
   </si>
@@ -31,6 +31,9 @@
   </si>
   <si>
     <t>Estimated date</t>
+  </si>
+  <si>
+    <t>Invoice date</t>
   </si>
   <si>
     <t>Payment date</t>
@@ -112,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -127,6 +130,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -351,8 +357,8 @@
     <col customWidth="1" min="3" max="3" width="38.25"/>
     <col customWidth="1" min="4" max="4" width="39.75"/>
     <col customWidth="1" min="5" max="5" width="17.25"/>
-    <col customWidth="1" min="6" max="7" width="16.38"/>
-    <col customWidth="1" min="8" max="8" width="13.13"/>
+    <col customWidth="1" min="6" max="8" width="16.38"/>
+    <col customWidth="1" min="9" max="9" width="13.13"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
@@ -364,7 +370,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="1"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" ht="15.75" customHeight="1"/>
     <row r="3" ht="15.75" customHeight="1">
@@ -380,7 +387,7 @@
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -389,12 +396,15 @@
       <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I3" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>1.0</v>
       </c>
-      <c r="H4" s="6">
+      <c r="I4" s="7">
         <v>250000.0</v>
       </c>
     </row>
